--- a/Запрещённые_предметы_июль_август.xlsx
+++ b/Запрещённые_предметы_июль_август.xlsx
@@ -19,13 +19,44 @@
 </workbook>
 </file>
 
+<file path=xl/comments1.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+  <authors>
+    <author>&lt;анонимный&gt;</author>
+  </authors>
+  <commentList>
+    <comment ref="A5" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <rFont val="Arial"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">Данные предоставлены пользователем.</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="H4" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <rFont val="Arial"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">Разница конверсий в процентных пунктах: 0.010 п.п. = на 1 изъятие больше на каждые 10 000 посетителей.</t>
+        </r>
+      </text>
+    </comment>
+  </commentList>
+</comments>
+</file>
+
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="29" uniqueCount="20">
-  <si>
-    <t xml:space="preserve">Запрещённые предметы: июль и август</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Конверсия = изъято / посетителей. Синие числа - исходные данные, остальное считается формулами.</t>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="33" uniqueCount="27">
+  <si>
+    <t xml:space="preserve">Конверсия = число изъятий / число посетителей за месяц. Синие числа - исходные данные, чёрные - формулы.</t>
   </si>
   <si>
     <t xml:space="preserve">Показатель</t>
@@ -37,7 +68,7 @@
     <t xml:space="preserve">Август</t>
   </si>
   <si>
-    <t xml:space="preserve">Изменение, август к июлю</t>
+    <t xml:space="preserve">Изменение (август к июлю)</t>
   </si>
   <si>
     <t xml:space="preserve">Кол-во</t>
@@ -46,40 +77,64 @@
     <t xml:space="preserve">Конверсия</t>
   </si>
   <si>
-    <t xml:space="preserve">Шт</t>
-  </si>
-  <si>
-    <t xml:space="preserve">%</t>
+    <t xml:space="preserve">Кол-во, шт</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Кол-во, %</t>
   </si>
   <si>
     <t xml:space="preserve">Конверсия, п.п.</t>
   </si>
   <si>
+    <t xml:space="preserve">Посетители, чел.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">—</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Оружие</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Колющее</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Аэрозоль</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Спирт</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Пиротехника</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Всего запрещённых</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Данные для графика (ссылки на таблицу выше)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Месяц</t>
+  </si>
+  <si>
     <t xml:space="preserve">Посетители</t>
   </si>
   <si>
-    <t xml:space="preserve">Оружие</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Колющее</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Аэрозоль</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Спирт</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Пиротехника</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Всего</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Данные графика (ссылки на таблицу)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Месяц</t>
+    <t xml:space="preserve">Конв. оружие</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Конв. колющее</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Конв. аэрозоль</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Конв. спирт</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Конв. пиротехника</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Конв. всего</t>
   </si>
 </sst>
 </file>
@@ -97,7 +152,7 @@
     <numFmt numFmtId="171" formatCode="\+0.0000;\-0.0000;0.0000"/>
     <numFmt numFmtId="172" formatCode="[&lt;0.00005]0.000%;[&lt;0.0005]0.00%;0.0%"/>
   </numFmts>
-  <fonts count="14">
+  <fonts count="13">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -121,15 +176,9 @@
       <family val="0"/>
     </font>
     <font>
-      <b val="true"/>
-      <sz val="13"/>
-      <name val="Arial"/>
-      <family val="0"/>
-      <charset val="1"/>
-    </font>
-    <font>
-      <sz val="9"/>
-      <color rgb="FF7F7F7F"/>
+      <i val="true"/>
+      <sz val="11"/>
+      <color rgb="FF595959"/>
       <name val="Arial"/>
       <family val="0"/>
       <charset val="1"/>
@@ -137,7 +186,7 @@
     <font>
       <b val="true"/>
       <sz val="11"/>
-      <color rgb="FF404040"/>
+      <color rgb="FFFFFFFF"/>
       <name val="Arial"/>
       <family val="0"/>
       <charset val="1"/>
@@ -163,32 +212,32 @@
       <charset val="1"/>
     </font>
     <font>
-      <b val="true"/>
-      <sz val="12"/>
-      <color rgb="FF262626"/>
+      <sz val="10"/>
       <name val="Arial"/>
       <family val="2"/>
     </font>
     <font>
-      <sz val="8"/>
-      <color rgb="FF404040"/>
-      <name val="Arial"/>
+      <b val="true"/>
+      <sz val="18"/>
+      <color rgb="FF000000"/>
+      <name val="Calibri"/>
       <family val="2"/>
     </font>
     <font>
-      <sz val="9"/>
-      <color rgb="FF262626"/>
-      <name val="Arial"/>
+      <sz val="10"/>
+      <color rgb="FF000000"/>
+      <name val="Calibri"/>
       <family val="2"/>
     </font>
     <font>
-      <sz val="9"/>
-      <color rgb="FF595959"/>
-      <name val="Arial"/>
+      <b val="true"/>
+      <sz val="10"/>
+      <color rgb="FF000000"/>
+      <name val="Calibri"/>
       <family val="2"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="5">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -197,12 +246,24 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor rgb="FFE7E7E7"/>
+        <fgColor rgb="FF1F4E78"/>
+        <bgColor rgb="FF003366"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD9E1F2"/>
+        <bgColor rgb="FFDDEBF7"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFCE4D6"/>
+        <bgColor rgb="FFDDEBF7"/>
       </patternFill>
     </fill>
   </fills>
-  <borders count="4">
+  <borders count="2">
     <border diagonalUp="false" diagonalDown="false">
       <left/>
       <right/>
@@ -211,30 +272,18 @@
       <diagonal/>
     </border>
     <border diagonalUp="false" diagonalDown="false">
-      <left/>
-      <right/>
-      <top/>
+      <left style="thin">
+        <color rgb="FFBFBFBF"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFBFBFBF"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFBFBFBF"/>
+      </top>
       <bottom style="thin">
-        <color rgb="FF7F7F7F"/>
+        <color rgb="FFBFBFBF"/>
       </bottom>
-      <diagonal/>
-    </border>
-    <border diagonalUp="false" diagonalDown="false">
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="thin">
-        <color rgb="FFD0D0D0"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border diagonalUp="false" diagonalDown="false">
-      <left/>
-      <right/>
-      <top style="thin">
-        <color rgb="FF7F7F7F"/>
-      </top>
-      <bottom/>
       <diagonal/>
     </border>
   </borders>
@@ -263,7 +312,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="22">
+  <cellXfs count="25">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -272,83 +321,95 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="5" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="6" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="165" fontId="7" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="8" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="166" fontId="8" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="167" fontId="8" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="166" fontId="9" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="168" fontId="8" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="167" fontId="9" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="169" fontId="8" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="168" fontId="9" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="165" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="169" fontId="9" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="170" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="9" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="167" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="170" fontId="9" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="168" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="171" fontId="9" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="171" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="7" fillId="0" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="166" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="7" fillId="0" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="169" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="166" fontId="7" fillId="0" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="6" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="167" fontId="7" fillId="0" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="165" fontId="6" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="168" fontId="7" fillId="0" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="166" fontId="6" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="169" fontId="7" fillId="0" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="167" fontId="6" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="9" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="165" fontId="9" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="168" fontId="6" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="169" fontId="6" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="165" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -364,8 +425,8 @@
   <colors>
     <indexedColors>
       <rgbColor rgb="FF000000"/>
-      <rgbColor rgb="FFF2F2F2"/>
-      <rgbColor rgb="FFFF0000"/>
+      <rgbColor rgb="FFFFFFFF"/>
+      <rgbColor rgb="FFC00000"/>
       <rgbColor rgb="FF00FF00"/>
       <rgbColor rgb="FF0000FF"/>
       <rgbColor rgb="FFFFFF00"/>
@@ -378,15 +439,15 @@
       <rgbColor rgb="FF800080"/>
       <rgbColor rgb="FF008080"/>
       <rgbColor rgb="FFBFBFBF"/>
-      <rgbColor rgb="FF7F7F7F"/>
+      <rgbColor rgb="FF878787"/>
       <rgbColor rgb="FF9999FF"/>
-      <rgbColor rgb="FF52514E"/>
-      <rgbColor rgb="FFE7E7E7"/>
-      <rgbColor rgb="FFCCFFFF"/>
+      <rgbColor rgb="FF7030A0"/>
+      <rgbColor rgb="FFFCE4D6"/>
+      <rgbColor rgb="FFDDEBF7"/>
       <rgbColor rgb="FF660066"/>
-      <rgbColor rgb="FFE87BA4"/>
+      <rgbColor rgb="FFFF8080"/>
       <rgbColor rgb="FF0066CC"/>
-      <rgbColor rgb="FFD0D0D0"/>
+      <rgbColor rgb="FFD9D9D9"/>
       <rgbColor rgb="FF000080"/>
       <rgbColor rgb="FFFF00FF"/>
       <rgbColor rgb="FFFFFF00"/>
@@ -396,29 +457,29 @@
       <rgbColor rgb="FF008080"/>
       <rgbColor rgb="FF0000FF"/>
       <rgbColor rgb="FF00CCFF"/>
-      <rgbColor rgb="FFCCFFFF"/>
+      <rgbColor rgb="FFD9E1F2"/>
       <rgbColor rgb="FFCCFFCC"/>
       <rgbColor rgb="FFFFFF99"/>
-      <rgbColor rgb="FF99CCFF"/>
+      <rgbColor rgb="FF9DC3E6"/>
       <rgbColor rgb="FFFF99CC"/>
       <rgbColor rgb="FFCC99FF"/>
       <rgbColor rgb="FFFFCC99"/>
-      <rgbColor rgb="FF2A78D6"/>
+      <rgbColor rgb="FF3366FF"/>
       <rgbColor rgb="FF33CCCC"/>
       <rgbColor rgb="FF99CC00"/>
       <rgbColor rgb="FFFFCC00"/>
       <rgbColor rgb="FFFF9900"/>
-      <rgbColor rgb="FFEB6834"/>
+      <rgbColor rgb="FFED7D31"/>
       <rgbColor rgb="FF595959"/>
-      <rgbColor rgb="FF969696"/>
+      <rgbColor rgb="FF70AD47"/>
       <rgbColor rgb="FF003366"/>
-      <rgbColor rgb="FF1BAF7A"/>
+      <rgbColor rgb="FF339966"/>
       <rgbColor rgb="FF003300"/>
-      <rgbColor rgb="FF404040"/>
+      <rgbColor rgb="FF333300"/>
       <rgbColor rgb="FF993300"/>
       <rgbColor rgb="FF993366"/>
-      <rgbColor rgb="FF4A3AA7"/>
-      <rgbColor rgb="FF262626"/>
+      <rgbColor rgb="FF1F4E78"/>
+      <rgbColor rgb="FF333333"/>
     </indexedColors>
   </colors>
 </styleSheet>
@@ -442,14 +503,14 @@
               </a:defRPr>
             </a:pPr>
             <a:r>
-              <a:rPr sz="1200" b="1" u="none" strike="noStrike">
+              <a:rPr sz="1800" b="1" u="none" strike="noStrike">
                 <a:solidFill>
-                  <a:srgbClr val="262626"/>
+                  <a:srgbClr val="000000"/>
                 </a:solidFill>
                 <a:uFillTx/>
-                <a:latin typeface="Arial"/>
+                <a:latin typeface="Calibri"/>
               </a:rPr>
-              <a:t>Конверсия запрещённых предметов, % от посетителей</a:t>
+              <a:t>Посетители и конверсия по месяцам</a:t>
             </a:r>
           </a:p>
         </c:rich>
@@ -464,31 +525,136 @@
     </c:title>
     <c:autoTitleDeleted val="0"/>
     <c:plotArea>
-      <c:lineChart>
-        <c:grouping val="standard"/>
+      <c:barChart>
+        <c:barDir val="col"/>
+        <c:grouping val="clustered"/>
         <c:varyColors val="0"/>
         <c:ser>
           <c:idx val="0"/>
           <c:order val="0"/>
           <c:tx>
             <c:strRef>
-              <c:f>Досмотр!H15</c:f>
+              <c:f>Досмотр!B14</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
-                  <c:v>Всего</c:v>
+                  <c:v>Посетители</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
           </c:tx>
           <c:spPr>
             <a:solidFill>
-              <a:srgbClr val="52514E"/>
+              <a:srgbClr val="DDEBF7"/>
             </a:solidFill>
-            <a:ln w="22320">
+            <a:ln w="12600">
               <a:solidFill>
-                <a:srgbClr val="52514E"/>
+                <a:srgbClr val="9DC3E6"/>
               </a:solidFill>
+              <a:round/>
+            </a:ln>
+          </c:spPr>
+          <c:invertIfNegative val="0"/>
+          <c:dLbls>
+            <c:txPr>
+              <a:bodyPr wrap="square"/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="1000" b="0" u="none" strike="noStrike">
+                    <a:solidFill>
+                      <a:srgbClr val="000000"/>
+                    </a:solidFill>
+                    <a:uFillTx/>
+                    <a:latin typeface="Calibri"/>
+                  </a:defRPr>
+                </a:pPr>
+              </a:p>
+            </c:txPr>
+            <c:dLblPos val="outEnd"/>
+            <c:showLegendKey val="0"/>
+            <c:showVal val="1"/>
+            <c:showCatName val="0"/>
+            <c:showSerName val="0"/>
+            <c:showPercent val="0"/>
+            <c:separator>; </c:separator>
+            <c:showLeaderLines val="1"/>
+            <c:leaderLines>
+              <c:spPr>
+                <a:ln w="0">
+                  <a:solidFill>
+                    <a:srgbClr val="9DC3E6"/>
+                  </a:solidFill>
+                </a:ln>
+              </c:spPr>
+            </c:leaderLines>
+            <c:extLst>
+              <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                <c15:showLeaderLines val="1"/>
+              </c:ext>
+            </c:extLst>
+          </c:dLbls>
+          <c:cat>
+            <c:strRef>
+              <c:f>Досмотр!$A$15:$A$16</c:f>
+              <c:strCache>
+                <c:ptCount val="2"/>
+                <c:pt idx="0">
+                  <c:v>Июль</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>Август</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>Досмотр!$B$15:$B$16</c:f>
+              <c:numCache>
+                <c:formatCode>#,##0</c:formatCode>
+                <c:ptCount val="2"/>
+                <c:pt idx="0">
+                  <c:v>436644</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>484265</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+        </c:ser>
+        <c:gapWidth val="60"/>
+        <c:overlap val="0"/>
+        <c:axId val="84505113"/>
+        <c:axId val="73450535"/>
+      </c:barChart>
+      <c:lineChart>
+        <c:grouping val="standard"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="1"/>
+          <c:order val="1"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>Досмотр!H14</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Конв. всего</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:srgbClr val="000000"/>
+            </a:solidFill>
+            <a:ln w="28440">
+              <a:solidFill>
+                <a:srgbClr val="000000"/>
+              </a:solidFill>
+              <a:prstDash val="dash"/>
               <a:round/>
             </a:ln>
           </c:spPr>
@@ -497,7 +663,7 @@
             <c:size val="7"/>
             <c:spPr>
               <a:solidFill>
-                <a:srgbClr val="52514E"/>
+                <a:srgbClr val="000000"/>
               </a:solidFill>
             </c:spPr>
           </c:marker>
@@ -507,12 +673,12 @@
               <a:lstStyle/>
               <a:p>
                 <a:pPr>
-                  <a:defRPr sz="800" b="0" u="none" strike="noStrike">
+                  <a:defRPr sz="1000" b="0" u="none" strike="noStrike">
                     <a:solidFill>
-                      <a:srgbClr val="404040"/>
+                      <a:srgbClr val="000000"/>
                     </a:solidFill>
                     <a:uFillTx/>
-                    <a:latin typeface="Arial"/>
+                    <a:latin typeface="Calibri"/>
                   </a:defRPr>
                 </a:pPr>
               </a:p>
@@ -527,7 +693,149 @@
             <c:showLeaderLines val="1"/>
             <c:leaderLines>
               <c:spPr>
-                <a:ln w="22320">
+                <a:ln w="28440">
+                  <a:solidFill>
+                    <a:srgbClr val="000000"/>
+                  </a:solidFill>
+                  <a:prstDash val="dash"/>
+                </a:ln>
+              </c:spPr>
+            </c:leaderLines>
+            <c:extLst>
+              <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                <c15:showLeaderLines val="1"/>
+              </c:ext>
+            </c:extLst>
+          </c:dLbls>
+          <c:cat>
+            <c:strRef>
+              <c:f>Досмотр!$A$15:$A$16</c:f>
+              <c:strCache>
+                <c:ptCount val="2"/>
+                <c:pt idx="0">
+                  <c:v>Июль</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>Август</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>Досмотр!$H$15:$H$16</c:f>
+              <c:numCache>
+                <c:formatCode>0.000%</c:formatCode>
+                <c:ptCount val="2"/>
+                <c:pt idx="0">
+                  <c:v>0.00729427176372514</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>0.00614126562935583</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="0"/>
+        </c:ser>
+        <c:ser>
+          <c:idx val="2"/>
+          <c:order val="2"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>Досмотр!D14</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Конв. колющее</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:srgbClr val="1F4E78"/>
+            </a:solidFill>
+            <a:ln w="28440">
+              <a:solidFill>
+                <a:srgbClr val="1F4E78"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="circle"/>
+            <c:size val="7"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:srgbClr val="1F4E78"/>
+              </a:solidFill>
+            </c:spPr>
+          </c:marker>
+          <c:dPt>
+            <c:idx val="0"/>
+            <c:marker>
+              <c:symbol val="circle"/>
+              <c:size val="7"/>
+              <c:spPr>
+                <a:solidFill>
+                  <a:srgbClr val="1F4E78"/>
+                </a:solidFill>
+              </c:spPr>
+            </c:marker>
+          </c:dPt>
+          <c:dLbls>
+            <c:dLbl>
+              <c:idx val="0"/>
+              <c:txPr>
+                <a:bodyPr wrap="square"/>
+                <a:lstStyle/>
+                <a:p>
+                  <a:pPr>
+                    <a:defRPr sz="1000" b="0" u="none" strike="noStrike">
+                      <a:solidFill>
+                        <a:srgbClr val="000000"/>
+                      </a:solidFill>
+                      <a:uFillTx/>
+                      <a:latin typeface="Calibri"/>
+                    </a:defRPr>
+                  </a:pPr>
+                </a:p>
+              </c:txPr>
+              <c:dLblPos val="t"/>
+              <c:showLegendKey val="0"/>
+              <c:showVal val="1"/>
+              <c:showCatName val="0"/>
+              <c:showSerName val="0"/>
+              <c:showPercent val="0"/>
+              <c:separator>; </c:separator>
+            </c:dLbl>
+            <c:txPr>
+              <a:bodyPr wrap="square"/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="1000" b="0" u="none" strike="noStrike">
+                    <a:solidFill>
+                      <a:srgbClr val="000000"/>
+                    </a:solidFill>
+                    <a:uFillTx/>
+                    <a:latin typeface="Calibri"/>
+                  </a:defRPr>
+                </a:pPr>
+              </a:p>
+            </c:txPr>
+            <c:dLblPos val="r"/>
+            <c:showLegendKey val="0"/>
+            <c:showVal val="1"/>
+            <c:showCatName val="0"/>
+            <c:showSerName val="0"/>
+            <c:showPercent val="0"/>
+            <c:separator>; </c:separator>
+            <c:showLeaderLines val="1"/>
+            <c:leaderLines>
+              <c:spPr>
+                <a:ln w="28440">
                   <a:solidFill>
                     <a:srgbClr val="000000"/>
                   </a:solidFill>
@@ -542,31 +850,29 @@
           </c:dLbls>
           <c:cat>
             <c:strRef>
-              <c:f>Досмотр!$A$16:$A$17</c:f>
+              <c:f>Досмотр!$A$15:$A$16</c:f>
               <c:strCache>
                 <c:ptCount val="2"/>
                 <c:pt idx="0">
-                  <c:v>Июль
-436 644 посетителей</c:v>
+                  <c:v>Июль</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>Август
-484 265 посетителей</c:v>
+                  <c:v>Август</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Досмотр!$H$16:$H$17</c:f>
+              <c:f>Досмотр!$D$15:$D$16</c:f>
               <c:numCache>
                 <c:formatCode>0.000%</c:formatCode>
                 <c:ptCount val="2"/>
                 <c:pt idx="0">
-                  <c:v>0.00729427176372514</c:v>
+                  <c:v>0.00392997499106824</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>0.00614126562935583</c:v>
+                  <c:v>0.00350634466665978</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -574,26 +880,26 @@
           <c:smooth val="0"/>
         </c:ser>
         <c:ser>
-          <c:idx val="1"/>
-          <c:order val="1"/>
+          <c:idx val="3"/>
+          <c:order val="3"/>
           <c:tx>
             <c:strRef>
-              <c:f>Досмотр!D15</c:f>
+              <c:f>Досмотр!E14</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
-                  <c:v>Колющее</c:v>
+                  <c:v>Конв. аэрозоль</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
           </c:tx>
           <c:spPr>
             <a:solidFill>
-              <a:srgbClr val="2A78D6"/>
+              <a:srgbClr val="70AD47"/>
             </a:solidFill>
-            <a:ln w="22320">
+            <a:ln w="28440">
               <a:solidFill>
-                <a:srgbClr val="2A78D6"/>
+                <a:srgbClr val="70AD47"/>
               </a:solidFill>
               <a:round/>
             </a:ln>
@@ -603,7 +909,7 @@
             <c:size val="7"/>
             <c:spPr>
               <a:solidFill>
-                <a:srgbClr val="2A78D6"/>
+                <a:srgbClr val="70AD47"/>
               </a:solidFill>
             </c:spPr>
           </c:marker>
@@ -613,12 +919,116 @@
               <a:lstStyle/>
               <a:p>
                 <a:pPr>
-                  <a:defRPr sz="800" b="0" u="none" strike="noStrike">
+                  <a:defRPr sz="1000" b="0" u="none" strike="noStrike">
                     <a:solidFill>
-                      <a:srgbClr val="404040"/>
+                      <a:srgbClr val="000000"/>
                     </a:solidFill>
                     <a:uFillTx/>
-                    <a:latin typeface="Arial"/>
+                    <a:latin typeface="Calibri"/>
+                  </a:defRPr>
+                </a:pPr>
+              </a:p>
+            </c:txPr>
+            <c:dLblPos val="t"/>
+            <c:showLegendKey val="0"/>
+            <c:showVal val="1"/>
+            <c:showCatName val="0"/>
+            <c:showSerName val="0"/>
+            <c:showPercent val="0"/>
+            <c:separator>; </c:separator>
+            <c:showLeaderLines val="1"/>
+            <c:leaderLines>
+              <c:spPr>
+                <a:ln w="28440">
+                  <a:solidFill>
+                    <a:srgbClr val="000000"/>
+                  </a:solidFill>
+                </a:ln>
+              </c:spPr>
+            </c:leaderLines>
+            <c:extLst>
+              <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                <c15:showLeaderLines val="1"/>
+              </c:ext>
+            </c:extLst>
+          </c:dLbls>
+          <c:cat>
+            <c:strRef>
+              <c:f>Досмотр!$A$15:$A$16</c:f>
+              <c:strCache>
+                <c:ptCount val="2"/>
+                <c:pt idx="0">
+                  <c:v>Июль</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>Август</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>Досмотр!$E$15:$E$16</c:f>
+              <c:numCache>
+                <c:formatCode>0.000%</c:formatCode>
+                <c:ptCount val="2"/>
+                <c:pt idx="0">
+                  <c:v>0.00199476003334524</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>0.00136495513819913</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="0"/>
+        </c:ser>
+        <c:ser>
+          <c:idx val="4"/>
+          <c:order val="4"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>Досмотр!F14</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Конв. спирт</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:srgbClr val="ED7D31"/>
+            </a:solidFill>
+            <a:ln w="28440">
+              <a:solidFill>
+                <a:srgbClr val="ED7D31"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="circle"/>
+            <c:size val="7"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:srgbClr val="ED7D31"/>
+              </a:solidFill>
+            </c:spPr>
+          </c:marker>
+          <c:dLbls>
+            <c:txPr>
+              <a:bodyPr wrap="square"/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="1000" b="0" u="none" strike="noStrike">
+                    <a:solidFill>
+                      <a:srgbClr val="000000"/>
+                    </a:solidFill>
+                    <a:uFillTx/>
+                    <a:latin typeface="Calibri"/>
                   </a:defRPr>
                 </a:pPr>
               </a:p>
@@ -633,7 +1043,7 @@
             <c:showLeaderLines val="1"/>
             <c:leaderLines>
               <c:spPr>
-                <a:ln w="22320">
+                <a:ln w="28440">
                   <a:solidFill>
                     <a:srgbClr val="000000"/>
                   </a:solidFill>
@@ -648,31 +1058,29 @@
           </c:dLbls>
           <c:cat>
             <c:strRef>
-              <c:f>Досмотр!$A$16:$A$17</c:f>
+              <c:f>Досмотр!$A$15:$A$16</c:f>
               <c:strCache>
                 <c:ptCount val="2"/>
                 <c:pt idx="0">
-                  <c:v>Июль
-436 644 посетителей</c:v>
+                  <c:v>Июль</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>Август
-484 265 посетителей</c:v>
+                  <c:v>Август</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Досмотр!$D$16:$D$17</c:f>
+              <c:f>Досмотр!$F$15:$F$16</c:f>
               <c:numCache>
                 <c:formatCode>0.000%</c:formatCode>
                 <c:ptCount val="2"/>
                 <c:pt idx="0">
-                  <c:v>0.00392997499106824</c:v>
+                  <c:v>0.00130312107804069</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>0.00350634466665978</c:v>
+                  <c:v>0.00119356137651905</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -680,26 +1088,26 @@
           <c:smooth val="0"/>
         </c:ser>
         <c:ser>
-          <c:idx val="2"/>
-          <c:order val="2"/>
+          <c:idx val="5"/>
+          <c:order val="5"/>
           <c:tx>
             <c:strRef>
-              <c:f>Досмотр!E15</c:f>
+              <c:f>Досмотр!C14</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
-                  <c:v>Аэрозоль</c:v>
+                  <c:v>Конв. оружие</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
           </c:tx>
           <c:spPr>
             <a:solidFill>
-              <a:srgbClr val="EB6834"/>
+              <a:srgbClr val="C00000"/>
             </a:solidFill>
-            <a:ln w="22320">
+            <a:ln w="28440">
               <a:solidFill>
-                <a:srgbClr val="EB6834"/>
+                <a:srgbClr val="C00000"/>
               </a:solidFill>
               <a:round/>
             </a:ln>
@@ -709,7 +1117,7 @@
             <c:size val="7"/>
             <c:spPr>
               <a:solidFill>
-                <a:srgbClr val="EB6834"/>
+                <a:srgbClr val="C00000"/>
               </a:solidFill>
             </c:spPr>
           </c:marker>
@@ -719,12 +1127,12 @@
               <a:lstStyle/>
               <a:p>
                 <a:pPr>
-                  <a:defRPr sz="800" b="0" u="none" strike="noStrike">
+                  <a:defRPr sz="1000" b="0" u="none" strike="noStrike">
                     <a:solidFill>
-                      <a:srgbClr val="404040"/>
+                      <a:srgbClr val="000000"/>
                     </a:solidFill>
                     <a:uFillTx/>
-                    <a:latin typeface="Arial"/>
+                    <a:latin typeface="Calibri"/>
                   </a:defRPr>
                 </a:pPr>
               </a:p>
@@ -739,7 +1147,7 @@
             <c:showLeaderLines val="1"/>
             <c:leaderLines>
               <c:spPr>
-                <a:ln w="22320">
+                <a:ln w="28440">
                   <a:solidFill>
                     <a:srgbClr val="000000"/>
                   </a:solidFill>
@@ -754,31 +1162,29 @@
           </c:dLbls>
           <c:cat>
             <c:strRef>
-              <c:f>Досмотр!$A$16:$A$17</c:f>
+              <c:f>Досмотр!$A$15:$A$16</c:f>
               <c:strCache>
                 <c:ptCount val="2"/>
                 <c:pt idx="0">
-                  <c:v>Июль
-436 644 посетителей</c:v>
+                  <c:v>Июль</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>Август
-484 265 посетителей</c:v>
+                  <c:v>Август</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Досмотр!$E$16:$E$17</c:f>
+              <c:f>Досмотр!$C$15:$C$16</c:f>
               <c:numCache>
-                <c:formatCode>0.000%</c:formatCode>
+                <c:formatCode>0.0000%</c:formatCode>
                 <c:ptCount val="2"/>
                 <c:pt idx="0">
-                  <c:v>0.00199476003334524</c:v>
+                  <c:v>5.49646851897656E-005</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>0.00136495513819913</c:v>
+                  <c:v>6.19495524144838E-005</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -786,26 +1192,26 @@
           <c:smooth val="0"/>
         </c:ser>
         <c:ser>
-          <c:idx val="3"/>
-          <c:order val="3"/>
+          <c:idx val="6"/>
+          <c:order val="6"/>
           <c:tx>
             <c:strRef>
-              <c:f>Досмотр!F15</c:f>
+              <c:f>Досмотр!G14</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
-                  <c:v>Спирт</c:v>
+                  <c:v>Конв. пиротехника</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
           </c:tx>
           <c:spPr>
             <a:solidFill>
-              <a:srgbClr val="1BAF7A"/>
+              <a:srgbClr val="7030A0"/>
             </a:solidFill>
-            <a:ln w="22320">
+            <a:ln w="28440">
               <a:solidFill>
-                <a:srgbClr val="1BAF7A"/>
+                <a:srgbClr val="7030A0"/>
               </a:solidFill>
               <a:round/>
             </a:ln>
@@ -815,7 +1221,7 @@
             <c:size val="7"/>
             <c:spPr>
               <a:solidFill>
-                <a:srgbClr val="1BAF7A"/>
+                <a:srgbClr val="7030A0"/>
               </a:solidFill>
             </c:spPr>
           </c:marker>
@@ -825,17 +1231,17 @@
               <a:lstStyle/>
               <a:p>
                 <a:pPr>
-                  <a:defRPr sz="800" b="0" u="none" strike="noStrike">
+                  <a:defRPr sz="1000" b="0" u="none" strike="noStrike">
                     <a:solidFill>
-                      <a:srgbClr val="404040"/>
+                      <a:srgbClr val="000000"/>
                     </a:solidFill>
                     <a:uFillTx/>
-                    <a:latin typeface="Arial"/>
+                    <a:latin typeface="Calibri"/>
                   </a:defRPr>
                 </a:pPr>
               </a:p>
             </c:txPr>
-            <c:dLblPos val="b"/>
+            <c:dLblPos val="t"/>
             <c:showLegendKey val="0"/>
             <c:showVal val="1"/>
             <c:showCatName val="0"/>
@@ -845,7 +1251,7 @@
             <c:showLeaderLines val="1"/>
             <c:leaderLines>
               <c:spPr>
-                <a:ln w="22320">
+                <a:ln w="28440">
                   <a:solidFill>
                     <a:srgbClr val="000000"/>
                   </a:solidFill>
@@ -860,235 +1266,21 @@
           </c:dLbls>
           <c:cat>
             <c:strRef>
-              <c:f>Досмотр!$A$16:$A$17</c:f>
+              <c:f>Досмотр!$A$15:$A$16</c:f>
               <c:strCache>
                 <c:ptCount val="2"/>
                 <c:pt idx="0">
-                  <c:v>Июль
-436 644 посетителей</c:v>
+                  <c:v>Июль</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>Август
-484 265 посетителей</c:v>
+                  <c:v>Август</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Досмотр!$F$16:$F$17</c:f>
-              <c:numCache>
-                <c:formatCode>0.000%</c:formatCode>
-                <c:ptCount val="2"/>
-                <c:pt idx="0">
-                  <c:v>0.00130312107804069</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>0.00119356137651905</c:v>
-                </c:pt>
-              </c:numCache>
-            </c:numRef>
-          </c:val>
-          <c:smooth val="0"/>
-        </c:ser>
-        <c:ser>
-          <c:idx val="4"/>
-          <c:order val="4"/>
-          <c:tx>
-            <c:strRef>
-              <c:f>Досмотр!C15</c:f>
-              <c:strCache>
-                <c:ptCount val="1"/>
-                <c:pt idx="0">
-                  <c:v>Оружие</c:v>
-                </c:pt>
-              </c:strCache>
-            </c:strRef>
-          </c:tx>
-          <c:spPr>
-            <a:solidFill>
-              <a:srgbClr val="4A3AA7"/>
-            </a:solidFill>
-            <a:ln w="22320">
-              <a:solidFill>
-                <a:srgbClr val="4A3AA7"/>
-              </a:solidFill>
-              <a:round/>
-            </a:ln>
-          </c:spPr>
-          <c:marker>
-            <c:symbol val="circle"/>
-            <c:size val="7"/>
-            <c:spPr>
-              <a:solidFill>
-                <a:srgbClr val="4A3AA7"/>
-              </a:solidFill>
-            </c:spPr>
-          </c:marker>
-          <c:dLbls>
-            <c:txPr>
-              <a:bodyPr wrap="square"/>
-              <a:lstStyle/>
-              <a:p>
-                <a:pPr>
-                  <a:defRPr sz="800" b="0" u="none" strike="noStrike">
-                    <a:solidFill>
-                      <a:srgbClr val="404040"/>
-                    </a:solidFill>
-                    <a:uFillTx/>
-                    <a:latin typeface="Arial"/>
-                  </a:defRPr>
-                </a:pPr>
-              </a:p>
-            </c:txPr>
-            <c:dLblPos val="t"/>
-            <c:showLegendKey val="0"/>
-            <c:showVal val="1"/>
-            <c:showCatName val="0"/>
-            <c:showSerName val="0"/>
-            <c:showPercent val="0"/>
-            <c:separator>; </c:separator>
-            <c:showLeaderLines val="1"/>
-            <c:leaderLines>
-              <c:spPr>
-                <a:ln w="22320">
-                  <a:solidFill>
-                    <a:srgbClr val="000000"/>
-                  </a:solidFill>
-                </a:ln>
-              </c:spPr>
-            </c:leaderLines>
-            <c:extLst>
-              <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
-                <c15:showLeaderLines val="1"/>
-              </c:ext>
-            </c:extLst>
-          </c:dLbls>
-          <c:cat>
-            <c:strRef>
-              <c:f>Досмотр!$A$16:$A$17</c:f>
-              <c:strCache>
-                <c:ptCount val="2"/>
-                <c:pt idx="0">
-                  <c:v>Июль
-436 644 посетителей</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>Август
-484 265 посетителей</c:v>
-                </c:pt>
-              </c:strCache>
-            </c:strRef>
-          </c:cat>
-          <c:val>
-            <c:numRef>
-              <c:f>Досмотр!$C$16:$C$17</c:f>
-              <c:numCache>
-                <c:formatCode>0.0000%</c:formatCode>
-                <c:ptCount val="2"/>
-                <c:pt idx="0">
-                  <c:v>5.49646851897656E-005</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>6.19495524144838E-005</c:v>
-                </c:pt>
-              </c:numCache>
-            </c:numRef>
-          </c:val>
-          <c:smooth val="0"/>
-        </c:ser>
-        <c:ser>
-          <c:idx val="5"/>
-          <c:order val="5"/>
-          <c:tx>
-            <c:strRef>
-              <c:f>Досмотр!G15</c:f>
-              <c:strCache>
-                <c:ptCount val="1"/>
-                <c:pt idx="0">
-                  <c:v>Пиротехника</c:v>
-                </c:pt>
-              </c:strCache>
-            </c:strRef>
-          </c:tx>
-          <c:spPr>
-            <a:solidFill>
-              <a:srgbClr val="E87BA4"/>
-            </a:solidFill>
-            <a:ln w="22320">
-              <a:solidFill>
-                <a:srgbClr val="E87BA4"/>
-              </a:solidFill>
-              <a:round/>
-            </a:ln>
-          </c:spPr>
-          <c:marker>
-            <c:symbol val="circle"/>
-            <c:size val="7"/>
-            <c:spPr>
-              <a:solidFill>
-                <a:srgbClr val="E87BA4"/>
-              </a:solidFill>
-            </c:spPr>
-          </c:marker>
-          <c:dLbls>
-            <c:txPr>
-              <a:bodyPr wrap="square"/>
-              <a:lstStyle/>
-              <a:p>
-                <a:pPr>
-                  <a:defRPr sz="800" b="0" u="none" strike="noStrike">
-                    <a:solidFill>
-                      <a:srgbClr val="404040"/>
-                    </a:solidFill>
-                    <a:uFillTx/>
-                    <a:latin typeface="Arial"/>
-                  </a:defRPr>
-                </a:pPr>
-              </a:p>
-            </c:txPr>
-            <c:dLblPos val="t"/>
-            <c:showLegendKey val="0"/>
-            <c:showVal val="1"/>
-            <c:showCatName val="0"/>
-            <c:showSerName val="0"/>
-            <c:showPercent val="0"/>
-            <c:separator>; </c:separator>
-            <c:showLeaderLines val="1"/>
-            <c:leaderLines>
-              <c:spPr>
-                <a:ln w="22320">
-                  <a:solidFill>
-                    <a:srgbClr val="000000"/>
-                  </a:solidFill>
-                </a:ln>
-              </c:spPr>
-            </c:leaderLines>
-            <c:extLst>
-              <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
-                <c15:showLeaderLines val="1"/>
-              </c:ext>
-            </c:extLst>
-          </c:dLbls>
-          <c:cat>
-            <c:strRef>
-              <c:f>Досмотр!$A$16:$A$17</c:f>
-              <c:strCache>
-                <c:ptCount val="2"/>
-                <c:pt idx="0">
-                  <c:v>Июль
-436 644 посетителей</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>Август
-484 265 посетителей</c:v>
-                </c:pt>
-              </c:strCache>
-            </c:strRef>
-          </c:cat>
-          <c:val>
-            <c:numRef>
-              <c:f>Досмотр!$G$16:$G$17</c:f>
+              <c:f>Досмотр!$G$15:$G$16</c:f>
               <c:numCache>
                 <c:formatCode>0.0000%</c:formatCode>
                 <c:ptCount val="2"/>
@@ -1111,11 +1303,11 @@
           </c:spPr>
         </c:hiLowLines>
         <c:marker val="1"/>
-        <c:axId val="6144806"/>
-        <c:axId val="73673485"/>
+        <c:axId val="10452423"/>
+        <c:axId val="34456913"/>
       </c:lineChart>
       <c:catAx>
-        <c:axId val="6144806"/>
+        <c:axId val="84505113"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -1128,7 +1320,7 @@
         <c:spPr>
           <a:ln w="9360">
             <a:solidFill>
-              <a:srgbClr val="BFBFBF"/>
+              <a:srgbClr val="878787"/>
             </a:solidFill>
             <a:round/>
           </a:ln>
@@ -1138,17 +1330,17 @@
           <a:lstStyle/>
           <a:p>
             <a:pPr>
-              <a:defRPr sz="900" b="0" u="none" strike="noStrike">
+              <a:defRPr sz="1000" b="0" u="none" strike="noStrike">
                 <a:solidFill>
-                  <a:srgbClr val="262626"/>
+                  <a:srgbClr val="000000"/>
                 </a:solidFill>
                 <a:uFillTx/>
-                <a:latin typeface="Arial"/>
+                <a:latin typeface="Calibri"/>
               </a:defRPr>
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="73673485"/>
+        <c:crossAx val="73450535"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -1156,7 +1348,121 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="73673485"/>
+        <c:axId val="73450535"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+          <c:max val="1000000"/>
+          <c:min val="0"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:title>
+          <c:tx>
+            <c:rich>
+              <a:bodyPr rot="-5400000"/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="1300" b="0" u="none" strike="noStrike">
+                    <a:uFillTx/>
+                    <a:latin typeface="Arial"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:r>
+                  <a:rPr sz="1000" b="1" u="none" strike="noStrike">
+                    <a:solidFill>
+                      <a:srgbClr val="000000"/>
+                    </a:solidFill>
+                    <a:uFillTx/>
+                    <a:latin typeface="Calibri"/>
+                  </a:rPr>
+                  <a:t>Посетители, чел.</a:t>
+                </a:r>
+              </a:p>
+            </c:rich>
+          </c:tx>
+          <c:overlay val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln w="0">
+              <a:noFill/>
+            </a:ln>
+          </c:spPr>
+        </c:title>
+        <c:numFmt formatCode="#,##0" sourceLinked="0"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:ln w="9360">
+            <a:solidFill>
+              <a:srgbClr val="878787"/>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="1000" b="0" u="none" strike="noStrike">
+                <a:solidFill>
+                  <a:srgbClr val="000000"/>
+                </a:solidFill>
+                <a:uFillTx/>
+                <a:latin typeface="Calibri"/>
+              </a:defRPr>
+            </a:pPr>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="84505113"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="between"/>
+      </c:valAx>
+      <c:catAx>
+        <c:axId val="10452423"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="t"/>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:ln w="9360">
+            <a:solidFill>
+              <a:srgbClr val="878787"/>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="1000" b="0" u="none" strike="noStrike">
+                <a:solidFill>
+                  <a:srgbClr val="000000"/>
+                </a:solidFill>
+                <a:uFillTx/>
+                <a:latin typeface="Calibri"/>
+              </a:defRPr>
+            </a:pPr>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="34456913"/>
+        <c:crosses val="autoZero"/>
+        <c:auto val="1"/>
+        <c:lblAlgn val="ctr"/>
+        <c:lblOffset val="100"/>
+        <c:noMultiLvlLbl val="0"/>
+      </c:catAx>
+      <c:valAx>
+        <c:axId val="34456913"/>
         <c:scaling>
           <c:logBase val="10"/>
           <c:orientation val="minMax"/>
@@ -1164,24 +1470,50 @@
           <c:min val="1E-005"/>
         </c:scaling>
         <c:delete val="0"/>
-        <c:axPos val="l"/>
-        <c:majorGridlines>
+        <c:axPos val="r"/>
+        <c:title>
+          <c:tx>
+            <c:rich>
+              <a:bodyPr rot="-5400000"/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="1300" b="0" u="none" strike="noStrike">
+                    <a:uFillTx/>
+                    <a:latin typeface="Arial"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:r>
+                  <a:rPr sz="1000" b="1" u="none" strike="noStrike">
+                    <a:solidFill>
+                      <a:srgbClr val="000000"/>
+                    </a:solidFill>
+                    <a:uFillTx/>
+                    <a:latin typeface="Calibri"/>
+                  </a:rPr>
+                  <a:t>Конверсия (логарифмическая шкала)</a:t>
+                </a:r>
+              </a:p>
+            </c:rich>
+          </c:tx>
+          <c:overlay val="0"/>
           <c:spPr>
-            <a:ln w="9360">
-              <a:solidFill>
-                <a:srgbClr val="E7E7E7"/>
-              </a:solidFill>
-              <a:round/>
+            <a:noFill/>
+            <a:ln w="0">
+              <a:noFill/>
             </a:ln>
           </c:spPr>
-        </c:majorGridlines>
+        </c:title>
         <c:numFmt formatCode="[&lt;0.00005]0.000%;[&lt;0.0005]0.00%;0.0%" sourceLinked="0"/>
         <c:majorTickMark val="none"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
         <c:spPr>
           <a:ln w="9360">
-            <a:noFill/>
+            <a:solidFill>
+              <a:srgbClr val="878787"/>
+            </a:solidFill>
+            <a:round/>
           </a:ln>
         </c:spPr>
         <c:txPr>
@@ -1189,18 +1521,18 @@
           <a:lstStyle/>
           <a:p>
             <a:pPr>
-              <a:defRPr sz="900" b="0" u="none" strike="noStrike">
+              <a:defRPr sz="1000" b="0" u="none" strike="noStrike">
                 <a:solidFill>
-                  <a:srgbClr val="595959"/>
+                  <a:srgbClr val="000000"/>
                 </a:solidFill>
                 <a:uFillTx/>
-                <a:latin typeface="Arial"/>
+                <a:latin typeface="Calibri"/>
               </a:defRPr>
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="6144806"/>
-        <c:crosses val="autoZero"/>
+        <c:crossAx val="10452423"/>
+        <c:crosses val="max"/>
         <c:crossBetween val="between"/>
       </c:valAx>
       <c:spPr>
@@ -1226,12 +1558,12 @@
         <a:lstStyle/>
         <a:p>
           <a:pPr>
-            <a:defRPr sz="900" b="0" u="none" strike="noStrike">
+            <a:defRPr sz="1000" b="0" u="none" strike="noStrike">
               <a:solidFill>
-                <a:srgbClr val="595959"/>
+                <a:srgbClr val="000000"/>
               </a:solidFill>
               <a:uFillTx/>
-              <a:latin typeface="Arial"/>
+              <a:latin typeface="Calibri"/>
             </a:defRPr>
           </a:pPr>
         </a:p>
@@ -1245,7 +1577,10 @@
       <a:srgbClr val="FFFFFF"/>
     </a:solidFill>
     <a:ln w="9360">
-      <a:noFill/>
+      <a:solidFill>
+        <a:srgbClr val="D9D9D9"/>
+      </a:solidFill>
+      <a:round/>
     </a:ln>
   </c:spPr>
 </c:chartSpace>
@@ -1473,13 +1808,13 @@
     <xdr:from>
       <xdr:col>0</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>19</xdr:row>
+      <xdr:row>18</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>7</xdr:col>
-      <xdr:colOff>448200</xdr:colOff>
-      <xdr:row>49</xdr:row>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>407880</xdr:colOff>
+      <xdr:row>48</xdr:row>
       <xdr:rowOff>44640</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame>
@@ -1488,8 +1823,8 @@
         <xdr:cNvGraphicFramePr/>
       </xdr:nvGraphicFramePr>
       <xdr:xfrm>
-        <a:off x="0" y="4125600"/>
-        <a:ext cx="7919640" cy="5759640"/>
+        <a:off x="0" y="3769920"/>
+        <a:ext cx="9359640" cy="5759640"/>
       </xdr:xfrm>
       <a:graphic>
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
@@ -1682,382 +2017,379 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="true"/>
   </sheetPr>
-  <dimension ref="A1:H17"/>
+  <dimension ref="A1:H16"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="22"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="2" style="0" width="14"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="2" style="0" width="15"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="2" t="s">
+    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A3" s="2" t="s">
         <v>1</v>
       </c>
+      <c r="B3" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="C3" s="2"/>
+      <c r="D3" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="E3" s="2"/>
+      <c r="F3" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="G3" s="2"/>
+      <c r="H3" s="2"/>
     </row>
-    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A4" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="B4" s="4" t="s">
-        <v>3</v>
-      </c>
-      <c r="C4" s="4"/>
-      <c r="D4" s="4" t="s">
-        <v>4</v>
-      </c>
-      <c r="E4" s="4"/>
-      <c r="F4" s="4" t="s">
+    <row r="4" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A4" s="2"/>
+      <c r="B4" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="G4" s="4"/>
-      <c r="H4" s="4"/>
+      <c r="C4" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D4" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="E4" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="F4" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="G4" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="H4" s="2" t="s">
+        <v>9</v>
+      </c>
     </row>
-    <row r="5" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A5" s="3"/>
-      <c r="B5" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="C5" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="D5" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="E5" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="F5" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="G5" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="H5" s="3" t="s">
+    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A5" s="3" t="s">
         <v>10</v>
+      </c>
+      <c r="B5" s="4" t="n">
+        <v>436644</v>
+      </c>
+      <c r="C5" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="D5" s="4" t="n">
+        <v>484265</v>
+      </c>
+      <c r="E5" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="F5" s="6" t="n">
+        <f aca="false">D5-B5</f>
+        <v>47621</v>
+      </c>
+      <c r="G5" s="7" t="n">
+        <f aca="false">IF(B5=0,"-",D5/B5-1)</f>
+        <v>0.109061386392576</v>
+      </c>
+      <c r="H5" s="8" t="s">
+        <v>11</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="B6" s="6" t="n">
-        <v>436644</v>
-      </c>
-      <c r="C6" s="7"/>
-      <c r="D6" s="6" t="n">
-        <v>484265</v>
-      </c>
-      <c r="E6" s="7"/>
-      <c r="F6" s="8" t="n">
+      <c r="A6" s="9" t="s">
+        <v>12</v>
+      </c>
+      <c r="B6" s="10" t="n">
+        <v>24</v>
+      </c>
+      <c r="C6" s="11" t="n">
+        <f aca="false">B6/$B$5</f>
+        <v>5.49646851897656E-005</v>
+      </c>
+      <c r="D6" s="10" t="n">
+        <v>30</v>
+      </c>
+      <c r="E6" s="11" t="n">
+        <f aca="false">D6/$D$5</f>
+        <v>6.19495524144838E-005</v>
+      </c>
+      <c r="F6" s="12" t="n">
         <f aca="false">D6-B6</f>
-        <v>47621</v>
-      </c>
-      <c r="G6" s="9" t="n">
+        <v>6</v>
+      </c>
+      <c r="G6" s="13" t="n">
         <f aca="false">IF(B6=0,"-",D6/B6-1)</f>
-        <v>0.109061386392576</v>
-      </c>
-      <c r="H6" s="10"/>
+        <v>0.25</v>
+      </c>
+      <c r="H6" s="14" t="n">
+        <f aca="false">(E6-C6)*100</f>
+        <v>0.000698486722471824</v>
+      </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="11" t="s">
-        <v>12</v>
-      </c>
-      <c r="B7" s="6" t="n">
-        <v>24</v>
-      </c>
-      <c r="C7" s="12" t="n">
-        <f aca="false">B7/$B$6</f>
-        <v>5.49646851897656E-005</v>
-      </c>
-      <c r="D7" s="6" t="n">
-        <v>30</v>
-      </c>
-      <c r="E7" s="12" t="n">
-        <f aca="false">D7/$D$6</f>
-        <v>6.19495524144838E-005</v>
-      </c>
-      <c r="F7" s="8" t="n">
+      <c r="A7" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="B7" s="10" t="n">
+        <v>1716</v>
+      </c>
+      <c r="C7" s="15" t="n">
+        <f aca="false">B7/$B$5</f>
+        <v>0.00392997499106824</v>
+      </c>
+      <c r="D7" s="10" t="n">
+        <v>1698</v>
+      </c>
+      <c r="E7" s="15" t="n">
+        <f aca="false">D7/$D$5</f>
+        <v>0.00350634466665978</v>
+      </c>
+      <c r="F7" s="12" t="n">
         <f aca="false">D7-B7</f>
-        <v>6</v>
-      </c>
-      <c r="G7" s="9" t="n">
+        <v>-18</v>
+      </c>
+      <c r="G7" s="13" t="n">
         <f aca="false">IF(B7=0,"-",D7/B7-1)</f>
-        <v>0.25</v>
-      </c>
-      <c r="H7" s="13" t="n">
+        <v>-0.0104895104895105</v>
+      </c>
+      <c r="H7" s="16" t="n">
         <f aca="false">(E7-C7)*100</f>
-        <v>0.000698486722471824</v>
+        <v>-0.0423630324408455</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="11" t="s">
-        <v>13</v>
-      </c>
-      <c r="B8" s="6" t="n">
-        <v>1716</v>
-      </c>
-      <c r="C8" s="7" t="n">
-        <f aca="false">B8/$B$6</f>
-        <v>0.00392997499106824</v>
-      </c>
-      <c r="D8" s="6" t="n">
-        <v>1698</v>
-      </c>
-      <c r="E8" s="7" t="n">
-        <f aca="false">D8/$D$6</f>
-        <v>0.00350634466665978</v>
-      </c>
-      <c r="F8" s="8" t="n">
+      <c r="A8" s="9" t="s">
+        <v>14</v>
+      </c>
+      <c r="B8" s="10" t="n">
+        <v>871</v>
+      </c>
+      <c r="C8" s="15" t="n">
+        <f aca="false">B8/$B$5</f>
+        <v>0.00199476003334524</v>
+      </c>
+      <c r="D8" s="10" t="n">
+        <v>661</v>
+      </c>
+      <c r="E8" s="15" t="n">
+        <f aca="false">D8/$D$5</f>
+        <v>0.00136495513819913</v>
+      </c>
+      <c r="F8" s="12" t="n">
         <f aca="false">D8-B8</f>
-        <v>-18</v>
-      </c>
-      <c r="G8" s="9" t="n">
+        <v>-210</v>
+      </c>
+      <c r="G8" s="13" t="n">
         <f aca="false">IF(B8=0,"-",D8/B8-1)</f>
-        <v>-0.0104895104895105</v>
-      </c>
-      <c r="H8" s="10" t="n">
+        <v>-0.241102181400689</v>
+      </c>
+      <c r="H8" s="16" t="n">
         <f aca="false">(E8-C8)*100</f>
-        <v>-0.0423630324408455</v>
+        <v>-0.0629804895146116</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="11" t="s">
-        <v>14</v>
-      </c>
-      <c r="B9" s="6" t="n">
-        <v>871</v>
-      </c>
-      <c r="C9" s="7" t="n">
-        <f aca="false">B9/$B$6</f>
-        <v>0.00199476003334524</v>
-      </c>
-      <c r="D9" s="6" t="n">
-        <v>661</v>
-      </c>
-      <c r="E9" s="7" t="n">
-        <f aca="false">D9/$D$6</f>
-        <v>0.00136495513819913</v>
-      </c>
-      <c r="F9" s="8" t="n">
+      <c r="A9" s="9" t="s">
+        <v>15</v>
+      </c>
+      <c r="B9" s="10" t="n">
+        <v>569</v>
+      </c>
+      <c r="C9" s="15" t="n">
+        <f aca="false">B9/$B$5</f>
+        <v>0.00130312107804069</v>
+      </c>
+      <c r="D9" s="10" t="n">
+        <v>578</v>
+      </c>
+      <c r="E9" s="15" t="n">
+        <f aca="false">D9/$D$5</f>
+        <v>0.00119356137651905</v>
+      </c>
+      <c r="F9" s="12" t="n">
         <f aca="false">D9-B9</f>
-        <v>-210</v>
-      </c>
-      <c r="G9" s="9" t="n">
+        <v>9</v>
+      </c>
+      <c r="G9" s="13" t="n">
         <f aca="false">IF(B9=0,"-",D9/B9-1)</f>
-        <v>-0.241102181400689</v>
-      </c>
-      <c r="H9" s="10" t="n">
+        <v>0.015817223198594</v>
+      </c>
+      <c r="H9" s="16" t="n">
         <f aca="false">(E9-C9)*100</f>
-        <v>-0.0629804895146116</v>
+        <v>-0.0109559701521637</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="11" t="s">
-        <v>15</v>
-      </c>
-      <c r="B10" s="6" t="n">
-        <v>569</v>
-      </c>
-      <c r="C10" s="7" t="n">
-        <f aca="false">B10/$B$6</f>
-        <v>0.00130312107804069</v>
-      </c>
-      <c r="D10" s="6" t="n">
-        <v>578</v>
-      </c>
-      <c r="E10" s="7" t="n">
-        <f aca="false">D10/$D$6</f>
-        <v>0.00119356137651905</v>
-      </c>
-      <c r="F10" s="8" t="n">
+      <c r="A10" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="B10" s="10" t="n">
+        <v>5</v>
+      </c>
+      <c r="C10" s="11" t="n">
+        <f aca="false">B10/$B$5</f>
+        <v>1.14509760812012E-005</v>
+      </c>
+      <c r="D10" s="10" t="n">
+        <v>7</v>
+      </c>
+      <c r="E10" s="11" t="n">
+        <f aca="false">D10/$D$5</f>
+        <v>1.44548955633796E-005</v>
+      </c>
+      <c r="F10" s="12" t="n">
         <f aca="false">D10-B10</f>
-        <v>9</v>
-      </c>
-      <c r="G10" s="9" t="n">
+        <v>2</v>
+      </c>
+      <c r="G10" s="13" t="n">
         <f aca="false">IF(B10=0,"-",D10/B10-1)</f>
-        <v>0.015817223198594</v>
-      </c>
-      <c r="H10" s="10" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="H10" s="14" t="n">
         <f aca="false">(E10-C10)*100</f>
-        <v>-0.0109559701521637</v>
+        <v>0.000300391948217839</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="11" t="s">
-        <v>16</v>
-      </c>
-      <c r="B11" s="6" t="n">
-        <v>5</v>
-      </c>
-      <c r="C11" s="12" t="n">
-        <f aca="false">B11/$B$6</f>
-        <v>1.14509760812012E-005</v>
-      </c>
-      <c r="D11" s="6" t="n">
-        <v>7</v>
-      </c>
-      <c r="E11" s="12" t="n">
-        <f aca="false">D11/$D$6</f>
-        <v>1.44548955633796E-005</v>
-      </c>
-      <c r="F11" s="8" t="n">
+      <c r="A11" s="17" t="s">
+        <v>17</v>
+      </c>
+      <c r="B11" s="18" t="n">
+        <f aca="false">SUM(B6:B10)</f>
+        <v>3185</v>
+      </c>
+      <c r="C11" s="19" t="n">
+        <f aca="false">B11/$B$5</f>
+        <v>0.00729427176372514</v>
+      </c>
+      <c r="D11" s="18" t="n">
+        <f aca="false">SUM(D6:D10)</f>
+        <v>2974</v>
+      </c>
+      <c r="E11" s="19" t="n">
+        <f aca="false">D11/$D$5</f>
+        <v>0.00614126562935583</v>
+      </c>
+      <c r="F11" s="20" t="n">
         <f aca="false">D11-B11</f>
-        <v>2</v>
-      </c>
-      <c r="G11" s="9" t="n">
+        <v>-211</v>
+      </c>
+      <c r="G11" s="21" t="n">
         <f aca="false">IF(B11=0,"-",D11/B11-1)</f>
-        <v>0.4</v>
-      </c>
-      <c r="H11" s="13" t="n">
+        <v>-0.0662480376766091</v>
+      </c>
+      <c r="H11" s="22" t="n">
         <f aca="false">(E11-C11)*100</f>
-        <v>0.000300391948217839</v>
+        <v>-0.115300613436931</v>
       </c>
     </row>
-    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="14" t="s">
-        <v>17</v>
-      </c>
-      <c r="B12" s="15" t="n">
-        <f aca="false">SUM(B7:B11)</f>
-        <v>3185</v>
-      </c>
-      <c r="C12" s="16" t="n">
-        <f aca="false">B12/$B$6</f>
-        <v>0.00729427176372514</v>
-      </c>
-      <c r="D12" s="15" t="n">
-        <f aca="false">SUM(D7:D11)</f>
-        <v>2974</v>
-      </c>
-      <c r="E12" s="16" t="n">
-        <f aca="false">D12/$D$6</f>
-        <v>0.00614126562935583</v>
-      </c>
-      <c r="F12" s="17" t="n">
-        <f aca="false">D12-B12</f>
-        <v>-211</v>
-      </c>
-      <c r="G12" s="18" t="n">
-        <f aca="false">IF(B12=0,"-",D12/B12-1)</f>
-        <v>-0.0662480376766091</v>
-      </c>
-      <c r="H12" s="19" t="n">
-        <f aca="false">(E12-C12)*100</f>
-        <v>-0.115300613436931</v>
+    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A13" s="23" t="s">
+        <v>18</v>
       </c>
     </row>
-    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="14" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="2" t="s">
-        <v>18</v>
+        <v>19</v>
+      </c>
+      <c r="B14" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="C14" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="D14" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="E14" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="F14" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="G14" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="H14" s="2" t="s">
+        <v>26</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="B15" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="C15" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="D15" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="E15" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="F15" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="G15" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="H15" s="3" t="s">
-        <v>17</v>
+      <c r="A15" s="9" t="s">
+        <v>2</v>
+      </c>
+      <c r="B15" s="24" t="n">
+        <f aca="false">B5</f>
+        <v>436644</v>
+      </c>
+      <c r="C15" s="11" t="n">
+        <f aca="false">C6</f>
+        <v>5.49646851897656E-005</v>
+      </c>
+      <c r="D15" s="15" t="n">
+        <f aca="false">C7</f>
+        <v>0.00392997499106824</v>
+      </c>
+      <c r="E15" s="15" t="n">
+        <f aca="false">C8</f>
+        <v>0.00199476003334524</v>
+      </c>
+      <c r="F15" s="15" t="n">
+        <f aca="false">C9</f>
+        <v>0.00130312107804069</v>
+      </c>
+      <c r="G15" s="11" t="n">
+        <f aca="false">C10</f>
+        <v>1.14509760812012E-005</v>
+      </c>
+      <c r="H15" s="15" t="n">
+        <f aca="false">C11</f>
+        <v>0.00729427176372514</v>
       </c>
     </row>
-    <row r="16" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A16" s="20" t="str">
-        <f aca="false">"Июль"&amp;CHAR(10)&amp;INT(B6/1000)&amp;" "&amp;TEXT(MOD(B6,1000),"000")&amp;" посетителей"</f>
-        <v>Июль
-436 644 посетителей</v>
-      </c>
-      <c r="B16" s="21" t="n">
-        <f aca="false">B6</f>
-        <v>436644</v>
-      </c>
-      <c r="C16" s="12" t="n">
-        <f aca="false">C7</f>
-        <v>5.49646851897656E-005</v>
-      </c>
-      <c r="D16" s="7" t="n">
-        <f aca="false">C8</f>
-        <v>0.00392997499106824</v>
-      </c>
-      <c r="E16" s="7" t="n">
-        <f aca="false">C9</f>
-        <v>0.00199476003334524</v>
-      </c>
-      <c r="F16" s="7" t="n">
-        <f aca="false">C10</f>
-        <v>0.00130312107804069</v>
-      </c>
-      <c r="G16" s="12" t="n">
-        <f aca="false">C11</f>
-        <v>1.14509760812012E-005</v>
-      </c>
-      <c r="H16" s="7" t="n">
-        <f aca="false">C12</f>
-        <v>0.00729427176372514</v>
-      </c>
-    </row>
-    <row r="17" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A17" s="20" t="str">
-        <f aca="false">"Август"&amp;CHAR(10)&amp;INT(D6/1000)&amp;" "&amp;TEXT(MOD(D6,1000),"000")&amp;" посетителей"</f>
-        <v>Август
-484 265 посетителей</v>
-      </c>
-      <c r="B17" s="21" t="n">
-        <f aca="false">D6</f>
+    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A16" s="9" t="s">
+        <v>3</v>
+      </c>
+      <c r="B16" s="24" t="n">
+        <f aca="false">D5</f>
         <v>484265</v>
       </c>
-      <c r="C17" s="12" t="n">
+      <c r="C16" s="11" t="n">
+        <f aca="false">E6</f>
+        <v>6.19495524144838E-005</v>
+      </c>
+      <c r="D16" s="15" t="n">
         <f aca="false">E7</f>
-        <v>6.19495524144838E-005</v>
-      </c>
-      <c r="D17" s="7" t="n">
+        <v>0.00350634466665978</v>
+      </c>
+      <c r="E16" s="15" t="n">
         <f aca="false">E8</f>
-        <v>0.00350634466665978</v>
-      </c>
-      <c r="E17" s="7" t="n">
+        <v>0.00136495513819913</v>
+      </c>
+      <c r="F16" s="15" t="n">
         <f aca="false">E9</f>
-        <v>0.00136495513819913</v>
-      </c>
-      <c r="F17" s="7" t="n">
+        <v>0.00119356137651905</v>
+      </c>
+      <c r="G16" s="11" t="n">
         <f aca="false">E10</f>
-        <v>0.00119356137651905</v>
-      </c>
-      <c r="G17" s="12" t="n">
+        <v>1.44548955633796E-005</v>
+      </c>
+      <c r="H16" s="15" t="n">
         <f aca="false">E11</f>
-        <v>1.44548955633796E-005</v>
-      </c>
-      <c r="H17" s="7" t="n">
-        <f aca="false">E12</f>
         <v>0.00614126562935583</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="4">
-    <mergeCell ref="A4:A5"/>
-    <mergeCell ref="B4:C4"/>
-    <mergeCell ref="D4:E4"/>
-    <mergeCell ref="F4:H4"/>
+    <mergeCell ref="A3:A4"/>
+    <mergeCell ref="B3:C3"/>
+    <mergeCell ref="D3:E3"/>
+    <mergeCell ref="F3:H3"/>
   </mergeCells>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
@@ -2066,6 +2398,7 @@
     <oddHeader/>
     <oddFooter/>
   </headerFooter>
-  <drawing r:id="rId1"/>
+  <drawing r:id="rId2"/>
+  <legacyDrawing r:id="rId3"/>
 </worksheet>
 </file>